--- a/branches/feat/2026/StructureDefinition-mii-pr-seltene-symptom-condition.xlsx
+++ b/branches/feat/2026/StructureDefinition-mii-pr-seltene-symptom-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T16:21:59+00:00</t>
+    <t>2026-07-28T16:11:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/2026/StructureDefinition-mii-pr-seltene-symptom-condition.xlsx
+++ b/branches/feat/2026/StructureDefinition-mii-pr-seltene-symptom-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T16:11:09+00:00</t>
+    <t>2026-07-28T16:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/2026/StructureDefinition-mii-pr-seltene-symptom-condition.xlsx
+++ b/branches/feat/2026/StructureDefinition-mii-pr-seltene-symptom-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T16:26:31+00:00</t>
+    <t>2026-07-28T16:41:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
